--- a/chapter_7/reductions-lit/data/dilution_data_extra.xlsx
+++ b/chapter_7/reductions-lit/data/dilution_data_extra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions-lit/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/chapter_7/reductions-lit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{A159C0DB-AC25-4DE9-8CEC-DA3CD6C5DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FB5D6F2-A512-4992-923B-0F2FB8CBFA4F}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{A159C0DB-AC25-4DE9-8CEC-DA3CD6C5DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E8377A3-26DA-4C4B-9465-44A6D16A7E81}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{122F0065-8602-49EC-B7E3-7261009AF15D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{122F0065-8602-49EC-B7E3-7261009AF15D}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="74">
   <si>
     <t>Table 5</t>
   </si>
@@ -255,6 +255,9 @@
   </si>
   <si>
     <t>1:1</t>
+  </si>
+  <si>
+    <t>dil.dm</t>
   </si>
 </sst>
 </file>
@@ -308,7 +311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -322,6 +325,12 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -659,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2755324F-EBFB-4825-BA7E-D1F948945CF9}">
-  <dimension ref="A1:O1048552"/>
+  <dimension ref="A1:P1048552"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -668,13 +677,15 @@
     <col min="4" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="4"/>
     <col min="9" max="9" width="9.140625" style="3"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>54</v>
       </c>
@@ -693,35 +704,38 @@
       <c r="F1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="10" t="s">
         <v>60</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -740,33 +754,37 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>3.96</v>
       </c>
       <c r="H2" s="4">
         <v>0.25</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
+        <f>G2*(1/(1+H2))</f>
+        <v>3.1680000000000001</v>
+      </c>
+      <c r="K2">
         <v>8.6</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>6.7</v>
       </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="1">
-        <f>(1-(K2/J2))*100</f>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1">
+        <f>(1-(L2/K2))*100</f>
         <v>22.093023255813947</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -785,33 +803,37 @@
       <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>2.4900000000000002</v>
       </c>
       <c r="H3" s="4">
         <v>0.5</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J39" si="0">G3*(1/(1+H3))</f>
+        <v>1.6600000000000001</v>
+      </c>
+      <c r="K3">
         <v>2.9</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>2</v>
       </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="1">
-        <f t="shared" ref="M3:M39" si="0">(1-(K3/J3))*100</f>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1">
+        <f t="shared" ref="N3:N39" si="1">(1-(L3/K3))*100</f>
         <v>31.034482758620683</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -830,7 +852,7 @@
       <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>2.4900000000000002</v>
       </c>
       <c r="H4" s="4">
@@ -839,27 +861,31 @@
       <c r="I4" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
+        <f t="shared" si="0"/>
+        <v>1.2450000000000001</v>
+      </c>
+      <c r="K4">
         <v>6</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>4</v>
       </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="1">
-        <f t="shared" si="0"/>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="1">
+        <f t="shared" si="1"/>
         <v>33.333333333333336</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -878,7 +904,7 @@
       <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>2.4900000000000002</v>
       </c>
       <c r="H5" s="4">
@@ -887,27 +913,31 @@
       <c r="I5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
+        <f t="shared" si="0"/>
+        <v>1.2450000000000001</v>
+      </c>
+      <c r="K5">
         <v>3.8</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1.6</v>
       </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="1">
-        <f t="shared" si="0"/>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="1">
+        <f t="shared" si="1"/>
         <v>57.894736842105267</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>67</v>
       </c>
@@ -926,7 +956,7 @@
       <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>4.7300000000000004</v>
       </c>
       <c r="H6" s="4">
@@ -935,24 +965,28 @@
       <c r="I6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
+        <f t="shared" si="0"/>
+        <v>2.3650000000000002</v>
+      </c>
+      <c r="K6">
         <v>35.200000000000003</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>35.1</v>
       </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="1">
-        <f t="shared" si="0"/>
+      <c r="M6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="1">
+        <f t="shared" si="1"/>
         <v>0.28409090909091717</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -971,7 +1005,7 @@
       <c r="F7" t="s">
         <v>10</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>4.7300000000000004</v>
       </c>
       <c r="H7" s="4">
@@ -980,24 +1014,28 @@
       <c r="I7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
+        <f t="shared" si="0"/>
+        <v>2.3650000000000002</v>
+      </c>
+      <c r="K7">
         <v>17.100000000000001</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>11.4</v>
       </c>
-      <c r="L7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="1">
-        <f t="shared" si="0"/>
+      <c r="M7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="1">
+        <f t="shared" si="1"/>
         <v>33.333333333333336</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -1016,27 +1054,31 @@
       <c r="F8" t="s">
         <v>23</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>10.5</v>
       </c>
       <c r="H8" s="4">
         <v>0.2</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+      <c r="K8">
         <v>26</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>24</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="1">
-        <f t="shared" si="0"/>
+      <c r="N8" s="1">
+        <f t="shared" si="1"/>
         <v>7.6923076923076872</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -1055,24 +1097,28 @@
       <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>10.5</v>
       </c>
       <c r="H9" s="4">
         <v>0.4</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="K9">
         <v>26</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>23</v>
       </c>
-      <c r="M9" s="1">
-        <f t="shared" si="0"/>
+      <c r="N9" s="1">
+        <f t="shared" si="1"/>
         <v>11.538461538461542</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -1091,24 +1137,28 @@
       <c r="F10" t="s">
         <v>23</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>10.5</v>
       </c>
       <c r="H10" s="4">
         <v>0.6</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
+        <f t="shared" si="0"/>
+        <v>6.5625</v>
+      </c>
+      <c r="K10">
         <v>26</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>17</v>
       </c>
-      <c r="M10" s="1">
-        <f t="shared" si="0"/>
+      <c r="N10" s="1">
+        <f t="shared" si="1"/>
         <v>34.615384615384613</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -1127,24 +1177,28 @@
       <c r="F11" t="s">
         <v>23</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>10.5</v>
       </c>
       <c r="H11" s="4">
         <v>0.8</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
+        <f t="shared" si="0"/>
+        <v>5.8333333333333339</v>
+      </c>
+      <c r="K11">
         <v>26</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>14</v>
       </c>
-      <c r="M11" s="1">
-        <f t="shared" si="0"/>
+      <c r="N11" s="1">
+        <f t="shared" si="1"/>
         <v>46.153846153846153</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -1163,7 +1217,7 @@
       <c r="F12" t="s">
         <v>23</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>10.5</v>
       </c>
       <c r="H12" s="4">
@@ -1172,18 +1226,22 @@
       <c r="I12" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
+        <f t="shared" si="0"/>
+        <v>5.25</v>
+      </c>
+      <c r="K12">
         <v>26</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>11</v>
       </c>
-      <c r="M12" s="1">
-        <f t="shared" si="0"/>
+      <c r="N12" s="1">
+        <f t="shared" si="1"/>
         <v>57.692307692307686</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -1202,24 +1260,28 @@
       <c r="F13" t="s">
         <v>23</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>10.5</v>
       </c>
       <c r="H13" s="4">
         <v>1.2</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
+        <f t="shared" si="0"/>
+        <v>4.7727272727272725</v>
+      </c>
+      <c r="K13">
         <v>26</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>12</v>
       </c>
-      <c r="M13" s="1">
-        <f t="shared" si="0"/>
+      <c r="N13" s="1">
+        <f t="shared" si="1"/>
         <v>53.846153846153847</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -1238,24 +1300,28 @@
       <c r="F14" t="s">
         <v>23</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>10.5</v>
       </c>
       <c r="H14" s="4">
         <v>1.4</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
+        <f t="shared" si="0"/>
+        <v>4.375</v>
+      </c>
+      <c r="K14">
         <v>26</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>8</v>
       </c>
-      <c r="M14" s="1">
-        <f t="shared" si="0"/>
+      <c r="N14" s="1">
+        <f t="shared" si="1"/>
         <v>69.230769230769226</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -1271,35 +1337,39 @@
       <c r="F15" t="s">
         <v>34</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>10.3</v>
       </c>
       <c r="H15" s="4">
         <v>0.5</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="1">
+        <f t="shared" si="0"/>
+        <v>6.8666666666666671</v>
+      </c>
+      <c r="K15" s="6">
         <f>267/2858*100</f>
         <v>9.3421973407977603</v>
       </c>
-      <c r="K15" s="6">
+      <c r="L15" s="6">
         <f>166/2858*100</f>
         <v>5.808257522743177</v>
       </c>
-      <c r="L15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="1">
-        <f t="shared" si="0"/>
+      <c r="M15" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" s="1">
+        <f t="shared" si="1"/>
         <v>37.827715355805246</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>0</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -1315,7 +1385,7 @@
       <c r="F16" t="s">
         <v>34</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>10.3</v>
       </c>
       <c r="H16" s="4">
@@ -1324,29 +1394,33 @@
       <c r="I16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="1">
+        <f t="shared" si="0"/>
+        <v>5.15</v>
+      </c>
+      <c r="K16" s="6">
         <f>267/2858*100</f>
         <v>9.3421973407977603</v>
       </c>
-      <c r="K16" s="6">
+      <c r="L16" s="6">
         <f>94/2858*100</f>
         <v>3.2890132960111966</v>
       </c>
-      <c r="L16" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="1">
-        <f t="shared" si="0"/>
+      <c r="M16" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" s="1">
+        <f t="shared" si="1"/>
         <v>64.794007490636702</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>0</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>69</v>
       </c>
@@ -1362,35 +1436,39 @@
       <c r="F17" t="s">
         <v>34</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>10.3</v>
       </c>
       <c r="H17" s="4">
         <v>1.5</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="1">
+        <f t="shared" si="0"/>
+        <v>4.12</v>
+      </c>
+      <c r="K17" s="6">
         <f>267/2858*100</f>
         <v>9.3421973407977603</v>
       </c>
-      <c r="K17" s="6">
+      <c r="L17" s="6">
         <f>55/2858*100</f>
         <v>1.9244226731980407</v>
       </c>
-      <c r="L17" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="1">
-        <f t="shared" si="0"/>
+      <c r="M17" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="1">
+        <f t="shared" si="1"/>
         <v>79.400749063670403</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>0</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -1406,35 +1484,39 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>10.3</v>
       </c>
       <c r="H18" s="4">
         <v>0.5</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="1">
+        <f t="shared" si="0"/>
+        <v>6.8666666666666671</v>
+      </c>
+      <c r="K18" s="6">
         <f>254/2858*100</f>
         <v>8.8873337998600412</v>
       </c>
-      <c r="K18" s="6">
+      <c r="L18" s="6">
         <f>168/2858*100</f>
         <v>5.8782365290412875</v>
       </c>
-      <c r="L18" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" s="1">
-        <f t="shared" si="0"/>
+      <c r="M18" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="1">
+        <f t="shared" si="1"/>
         <v>33.85826771653543</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>0</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -1450,7 +1532,7 @@
       <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>10.3</v>
       </c>
       <c r="H19" s="4">
@@ -1459,29 +1541,33 @@
       <c r="I19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="1">
+        <f t="shared" si="0"/>
+        <v>5.15</v>
+      </c>
+      <c r="K19" s="6">
         <f>254/2858*100</f>
         <v>8.8873337998600412</v>
       </c>
-      <c r="K19" s="6">
+      <c r="L19" s="6">
         <f>91/2858*100</f>
         <v>3.1840447865640309</v>
       </c>
-      <c r="L19" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="1">
-        <f t="shared" si="0"/>
+      <c r="M19" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="1">
+        <f t="shared" si="1"/>
         <v>64.173228346456696</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>0</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -1497,35 +1583,39 @@
       <c r="F20" t="s">
         <v>34</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>10.3</v>
       </c>
       <c r="H20" s="4">
         <v>1.5</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="1">
+        <f t="shared" si="0"/>
+        <v>4.12</v>
+      </c>
+      <c r="K20" s="6">
         <f>254/2858*100</f>
         <v>8.8873337998600412</v>
       </c>
-      <c r="K20" s="6">
+      <c r="L20" s="6">
         <f>58/2858*100</f>
         <v>2.0293911826452065</v>
       </c>
-      <c r="L20" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="1">
-        <f t="shared" si="0"/>
+      <c r="M20" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="1">
+        <f t="shared" si="1"/>
         <v>77.165354330708652</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>0</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>69</v>
       </c>
@@ -1541,35 +1631,39 @@
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>10.3</v>
       </c>
       <c r="H21" s="4">
         <v>0.5</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="1">
+        <f t="shared" si="0"/>
+        <v>6.8666666666666671</v>
+      </c>
+      <c r="K21" s="6">
         <f>174/2858*100</f>
         <v>6.0881735479356189</v>
       </c>
-      <c r="K21" s="6">
+      <c r="L21" s="6">
         <f>148/2858*100</f>
         <v>5.1784464660601817</v>
       </c>
-      <c r="L21" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" s="1">
-        <f t="shared" si="0"/>
+      <c r="M21" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" s="1">
+        <f t="shared" si="1"/>
         <v>14.942528735632187</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>0</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -1585,7 +1679,7 @@
       <c r="F22" t="s">
         <v>34</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>10.3</v>
       </c>
       <c r="H22" s="4">
@@ -1594,29 +1688,33 @@
       <c r="I22" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="1">
+        <f t="shared" si="0"/>
+        <v>5.15</v>
+      </c>
+      <c r="K22" s="6">
         <f>174/2858*100</f>
         <v>6.0881735479356189</v>
       </c>
-      <c r="K22" s="6">
+      <c r="L22" s="6">
         <f>97/2858*100</f>
         <v>3.3939818054583624</v>
       </c>
-      <c r="L22" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" s="1">
-        <f t="shared" si="0"/>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" s="1">
+        <f t="shared" si="1"/>
         <v>44.252873563218387</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>0</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -1632,35 +1730,39 @@
       <c r="F23" t="s">
         <v>34</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>10.3</v>
       </c>
       <c r="H23" s="4">
         <v>1.5</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="1">
+        <f t="shared" si="0"/>
+        <v>4.12</v>
+      </c>
+      <c r="K23" s="6">
         <f>174/2858*100</f>
         <v>6.0881735479356189</v>
       </c>
-      <c r="K23" s="6">
+      <c r="L23" s="6">
         <f>66/2858*100</f>
         <v>2.3093072078376489</v>
       </c>
-      <c r="L23" t="s">
-        <v>25</v>
-      </c>
-      <c r="M23" s="1">
-        <f t="shared" si="0"/>
+      <c r="M23" t="s">
+        <v>25</v>
+      </c>
+      <c r="N23" s="1">
+        <f t="shared" si="1"/>
         <v>62.068965517241367</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>0</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -1676,35 +1778,39 @@
       <c r="F24" t="s">
         <v>34</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>10.3</v>
       </c>
       <c r="H24" s="4">
         <v>0.5</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="1">
+        <f t="shared" si="0"/>
+        <v>6.8666666666666671</v>
+      </c>
+      <c r="K24" s="6">
         <f>118/2858*100</f>
         <v>4.1287613715885234</v>
       </c>
-      <c r="K24" s="6">
+      <c r="L24" s="6">
         <f>92/2858*100</f>
         <v>3.2190342897130861</v>
       </c>
-      <c r="L24" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" s="1">
-        <f t="shared" si="0"/>
+      <c r="M24" t="s">
+        <v>25</v>
+      </c>
+      <c r="N24" s="1">
+        <f t="shared" si="1"/>
         <v>22.033898305084744</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>0</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>69</v>
       </c>
@@ -1720,7 +1826,7 @@
       <c r="F25" t="s">
         <v>34</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>10.3</v>
       </c>
       <c r="H25" s="4">
@@ -1729,29 +1835,33 @@
       <c r="I25" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="1">
+        <f t="shared" si="0"/>
+        <v>5.15</v>
+      </c>
+      <c r="K25" s="6">
         <f>118/2858*100</f>
         <v>4.1287613715885234</v>
       </c>
-      <c r="K25" s="6">
+      <c r="L25" s="6">
         <f>59/2858*100</f>
         <v>2.0643806857942617</v>
       </c>
-      <c r="L25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M25" s="1">
-        <f t="shared" si="0"/>
+      <c r="M25" t="s">
+        <v>25</v>
+      </c>
+      <c r="N25" s="1">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -1767,35 +1877,39 @@
       <c r="F26" t="s">
         <v>34</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>10.3</v>
       </c>
       <c r="H26" s="4">
         <v>1.5</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="1">
+        <f t="shared" si="0"/>
+        <v>4.12</v>
+      </c>
+      <c r="K26" s="6">
         <f>118/2858*100</f>
         <v>4.1287613715885234</v>
       </c>
-      <c r="K26" s="6">
+      <c r="L26" s="6">
         <f>48/2858*100</f>
         <v>1.6794961511546536</v>
       </c>
-      <c r="L26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" s="1">
-        <f t="shared" si="0"/>
+      <c r="M26" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" s="1">
+        <f t="shared" si="1"/>
         <v>59.322033898305079</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>0</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -1808,33 +1922,37 @@
       <c r="F27" t="s">
         <v>34</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>8</v>
       </c>
       <c r="H27" s="4">
         <v>0.5</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
+        <f t="shared" si="0"/>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="K27">
         <v>37</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>24</v>
       </c>
-      <c r="L27" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" s="1">
-        <f t="shared" si="0"/>
+      <c r="M27" t="s">
+        <v>25</v>
+      </c>
+      <c r="N27" s="1">
+        <f t="shared" si="1"/>
         <v>35.13513513513513</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -1847,7 +1965,7 @@
       <c r="F28" t="s">
         <v>34</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>8</v>
       </c>
       <c r="H28" s="4">
@@ -1856,27 +1974,31 @@
       <c r="I28" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="K28">
         <v>37</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>23</v>
       </c>
-      <c r="L28" t="s">
-        <v>25</v>
-      </c>
-      <c r="M28" s="1">
-        <f t="shared" si="0"/>
+      <c r="M28" t="s">
+        <v>25</v>
+      </c>
+      <c r="N28" s="1">
+        <f t="shared" si="1"/>
         <v>37.837837837837839</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1889,33 +2011,37 @@
       <c r="F29" t="s">
         <v>34</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>8</v>
       </c>
       <c r="H29" s="4">
         <v>2</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="K29">
         <v>37</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>15</v>
       </c>
-      <c r="L29" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" s="1">
-        <f t="shared" si="0"/>
+      <c r="M29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N29" s="1">
+        <f t="shared" si="1"/>
         <v>59.459459459459453</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -1928,33 +2054,37 @@
       <c r="F30" t="s">
         <v>34</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>8</v>
       </c>
       <c r="H30" s="4">
         <v>0.5</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
+        <f t="shared" si="0"/>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="K30">
         <v>40</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>28</v>
       </c>
-      <c r="L30" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" s="1">
-        <f t="shared" si="0"/>
+      <c r="M30" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="1">
+        <f t="shared" si="1"/>
         <v>30.000000000000004</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1967,7 +2097,7 @@
       <c r="F31" t="s">
         <v>34</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>8</v>
       </c>
       <c r="H31" s="4">
@@ -1976,27 +2106,31 @@
       <c r="I31" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="K31">
         <v>40</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>26</v>
       </c>
-      <c r="L31" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" s="1">
-        <f t="shared" si="0"/>
+      <c r="M31" t="s">
+        <v>25</v>
+      </c>
+      <c r="N31" s="1">
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="O31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2009,33 +2143,37 @@
       <c r="F32" t="s">
         <v>34</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>8</v>
       </c>
       <c r="H32" s="4">
         <v>2</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="K32">
         <v>40</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>18</v>
       </c>
-      <c r="L32" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" s="1">
-        <f t="shared" si="0"/>
+      <c r="M32" t="s">
+        <v>25</v>
+      </c>
+      <c r="N32" s="1">
+        <f t="shared" si="1"/>
         <v>55.000000000000007</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="O32" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -2048,33 +2186,37 @@
       <c r="F33" t="s">
         <v>34</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>8</v>
       </c>
       <c r="H33" s="4">
         <v>0.5</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="1">
+        <f t="shared" si="0"/>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="K33">
         <v>46</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>33</v>
       </c>
-      <c r="L33" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" s="1">
-        <f t="shared" si="0"/>
+      <c r="M33" t="s">
+        <v>25</v>
+      </c>
+      <c r="N33" s="1">
+        <f t="shared" si="1"/>
         <v>28.260869565217394</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="O33" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -2087,7 +2229,7 @@
       <c r="F34" t="s">
         <v>34</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>8</v>
       </c>
       <c r="H34" s="4">
@@ -2096,27 +2238,31 @@
       <c r="I34" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="K34">
         <v>46</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>31</v>
       </c>
-      <c r="L34" t="s">
-        <v>25</v>
-      </c>
-      <c r="M34" s="1">
-        <f t="shared" si="0"/>
+      <c r="M34" t="s">
+        <v>25</v>
+      </c>
+      <c r="N34" s="1">
+        <f t="shared" si="1"/>
         <v>32.608695652173914</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -2129,33 +2275,37 @@
       <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="1">
         <v>8</v>
       </c>
       <c r="H35" s="4">
         <v>2</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="K35">
         <v>46</v>
       </c>
-      <c r="K35">
-        <v>25</v>
-      </c>
-      <c r="L35" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" s="1">
-        <f t="shared" si="0"/>
+      <c r="L35">
+        <v>25</v>
+      </c>
+      <c r="M35" t="s">
+        <v>25</v>
+      </c>
+      <c r="N35" s="1">
+        <f t="shared" si="1"/>
         <v>45.652173913043484</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="O35" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -2168,7 +2318,7 @@
       <c r="F36" t="s">
         <v>34</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="1">
         <v>7.4</v>
       </c>
       <c r="H36" s="4">
@@ -2177,24 +2327,28 @@
       <c r="I36" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="1">
+        <f t="shared" si="0"/>
+        <v>3.7</v>
+      </c>
+      <c r="K36">
         <v>17</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>7</v>
       </c>
-      <c r="L36" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" s="1">
-        <f t="shared" si="0"/>
+      <c r="M36" t="s">
+        <v>25</v>
+      </c>
+      <c r="N36" s="1">
+        <f t="shared" si="1"/>
         <v>58.82352941176471</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="O36" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -2207,7 +2361,7 @@
       <c r="F37" t="s">
         <v>34</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="1">
         <v>7.4</v>
       </c>
       <c r="H37" s="4">
@@ -2216,24 +2370,28 @@
       <c r="I37" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="1">
+        <f t="shared" si="0"/>
+        <v>3.7</v>
+      </c>
+      <c r="K37">
         <v>3</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>1</v>
       </c>
-      <c r="L37" t="s">
-        <v>25</v>
-      </c>
-      <c r="M37" s="1">
-        <f t="shared" si="0"/>
+      <c r="M37" t="s">
+        <v>25</v>
+      </c>
+      <c r="N37" s="1">
+        <f t="shared" si="1"/>
         <v>66.666666666666671</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="O37" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>70</v>
       </c>
@@ -2246,7 +2404,7 @@
       <c r="F38" t="s">
         <v>34</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="1">
         <v>7.4</v>
       </c>
       <c r="H38" s="4">
@@ -2255,24 +2413,28 @@
       <c r="I38" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="1">
+        <f t="shared" si="0"/>
+        <v>3.7</v>
+      </c>
+      <c r="K38">
         <v>10</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>5</v>
       </c>
-      <c r="L38" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" s="1">
-        <f t="shared" si="0"/>
+      <c r="M38" t="s">
+        <v>25</v>
+      </c>
+      <c r="N38" s="1">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="O38" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>70</v>
       </c>
@@ -2285,7 +2447,7 @@
       <c r="F39" t="s">
         <v>34</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="1">
         <v>7.4</v>
       </c>
       <c r="H39" s="4">
@@ -2294,20 +2456,24 @@
       <c r="I39" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="1">
+        <f t="shared" si="0"/>
+        <v>3.7</v>
+      </c>
+      <c r="K39">
         <v>22</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>8</v>
       </c>
-      <c r="L39" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" s="1">
-        <f t="shared" si="0"/>
+      <c r="M39" t="s">
+        <v>25</v>
+      </c>
+      <c r="N39" s="1">
+        <f t="shared" si="1"/>
         <v>63.636363636363633</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="O39" s="1" t="s">
         <v>46</v>
       </c>
     </row>

--- a/chapter_7/reductions-lit/data/dilution_data_extra.xlsx
+++ b/chapter_7/reductions-lit/data/dilution_data_extra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/chapter_7/reductions-lit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{A159C0DB-AC25-4DE9-8CEC-DA3CD6C5DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E8377A3-26DA-4C4B-9465-44A6D16A7E81}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{A159C0DB-AC25-4DE9-8CEC-DA3CD6C5DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753B993C-4716-4EFF-8DE0-11752B70EF3B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{122F0065-8602-49EC-B7E3-7261009AF15D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="84">
   <si>
     <t>Table 5</t>
   </si>
@@ -258,6 +258,36 @@
   </si>
   <si>
     <t>dil.dm</t>
+  </si>
+  <si>
+    <t>1:0.25</t>
+  </si>
+  <si>
+    <t>1:0.5</t>
+  </si>
+  <si>
+    <t>1:0.2</t>
+  </si>
+  <si>
+    <t>1:0.4</t>
+  </si>
+  <si>
+    <t>1:0.6</t>
+  </si>
+  <si>
+    <t>1:0.8</t>
+  </si>
+  <si>
+    <t>1:1.2</t>
+  </si>
+  <si>
+    <t>1:1.4</t>
+  </si>
+  <si>
+    <t>1:1.5</t>
+  </si>
+  <si>
+    <t>1:2</t>
   </si>
 </sst>
 </file>
@@ -760,6 +790,9 @@
       <c r="H2" s="4">
         <v>0.25</v>
       </c>
+      <c r="I2" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="J2" s="1">
         <f>G2*(1/(1+H2))</f>
         <v>3.1680000000000001</v>
@@ -809,6 +842,9 @@
       <c r="H3" s="4">
         <v>0.5</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="J3" s="1">
         <f t="shared" ref="J3:J39" si="0">G3*(1/(1+H3))</f>
         <v>1.6600000000000001</v>
@@ -1060,6 +1096,9 @@
       <c r="H8" s="4">
         <v>0.2</v>
       </c>
+      <c r="I8" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="J8" s="1">
         <f t="shared" si="0"/>
         <v>8.75</v>
@@ -1103,6 +1142,9 @@
       <c r="H9" s="4">
         <v>0.4</v>
       </c>
+      <c r="I9" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="J9" s="1">
         <f t="shared" si="0"/>
         <v>7.5</v>
@@ -1143,6 +1185,9 @@
       <c r="H10" s="4">
         <v>0.6</v>
       </c>
+      <c r="I10" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="J10" s="1">
         <f t="shared" si="0"/>
         <v>6.5625</v>
@@ -1183,6 +1228,9 @@
       <c r="H11" s="4">
         <v>0.8</v>
       </c>
+      <c r="I11" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="J11" s="1">
         <f t="shared" si="0"/>
         <v>5.8333333333333339</v>
@@ -1266,6 +1314,9 @@
       <c r="H13" s="4">
         <v>1.2</v>
       </c>
+      <c r="I13" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="J13" s="1">
         <f t="shared" si="0"/>
         <v>4.7727272727272725</v>
@@ -1306,6 +1357,9 @@
       <c r="H14" s="4">
         <v>1.4</v>
       </c>
+      <c r="I14" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="J14" s="1">
         <f t="shared" si="0"/>
         <v>4.375</v>
@@ -1343,6 +1397,9 @@
       <c r="H15" s="4">
         <v>0.5</v>
       </c>
+      <c r="I15" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="J15" s="1">
         <f t="shared" si="0"/>
         <v>6.8666666666666671</v>
@@ -1442,6 +1499,9 @@
       <c r="H17" s="4">
         <v>1.5</v>
       </c>
+      <c r="I17" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="J17" s="1">
         <f t="shared" si="0"/>
         <v>4.12</v>
@@ -1490,6 +1550,9 @@
       <c r="H18" s="4">
         <v>0.5</v>
       </c>
+      <c r="I18" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="J18" s="1">
         <f t="shared" si="0"/>
         <v>6.8666666666666671</v>
@@ -1589,6 +1652,9 @@
       <c r="H20" s="4">
         <v>1.5</v>
       </c>
+      <c r="I20" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="J20" s="1">
         <f t="shared" si="0"/>
         <v>4.12</v>
@@ -1637,6 +1703,9 @@
       <c r="H21" s="4">
         <v>0.5</v>
       </c>
+      <c r="I21" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="J21" s="1">
         <f t="shared" si="0"/>
         <v>6.8666666666666671</v>
@@ -1736,6 +1805,9 @@
       <c r="H23" s="4">
         <v>1.5</v>
       </c>
+      <c r="I23" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="J23" s="1">
         <f t="shared" si="0"/>
         <v>4.12</v>
@@ -1784,6 +1856,9 @@
       <c r="H24" s="4">
         <v>0.5</v>
       </c>
+      <c r="I24" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="J24" s="1">
         <f t="shared" si="0"/>
         <v>6.8666666666666671</v>
@@ -1883,6 +1958,9 @@
       <c r="H26" s="4">
         <v>1.5</v>
       </c>
+      <c r="I26" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="J26" s="1">
         <f t="shared" si="0"/>
         <v>4.12</v>
@@ -1928,6 +2006,9 @@
       <c r="H27" s="4">
         <v>0.5</v>
       </c>
+      <c r="I27" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="J27" s="1">
         <f t="shared" si="0"/>
         <v>5.333333333333333</v>
@@ -2017,6 +2098,9 @@
       <c r="H29" s="4">
         <v>2</v>
       </c>
+      <c r="I29" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="J29" s="1">
         <f t="shared" si="0"/>
         <v>2.6666666666666665</v>
@@ -2060,6 +2144,9 @@
       <c r="H30" s="4">
         <v>0.5</v>
       </c>
+      <c r="I30" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="J30" s="1">
         <f t="shared" si="0"/>
         <v>5.333333333333333</v>
@@ -2149,6 +2236,9 @@
       <c r="H32" s="4">
         <v>2</v>
       </c>
+      <c r="I32" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="J32" s="1">
         <f t="shared" si="0"/>
         <v>2.6666666666666665</v>
@@ -2192,6 +2282,9 @@
       <c r="H33" s="4">
         <v>0.5</v>
       </c>
+      <c r="I33" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="J33" s="1">
         <f t="shared" si="0"/>
         <v>5.333333333333333</v>
@@ -2280,6 +2373,9 @@
       </c>
       <c r="H35" s="4">
         <v>2</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" si="0"/>
